--- a/Raj-tensile-structure.xlsx
+++ b/Raj-tensile-structure.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LC-148\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LC-148\Desktop\Raj-tensile-structure\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenario" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="401">
   <si>
     <t>Product name:- Raj Tensile Structure
 created by :Uncodemy 
@@ -721,9 +721,6 @@
     </r>
   </si>
   <si>
-    <t>Vidhya</t>
-  </si>
-  <si>
     <t>Bhagyashree</t>
   </si>
   <si>
@@ -755,9 +752,6 @@
   </si>
   <si>
     <t>User should be able to click on services dropdown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pass </t>
   </si>
   <si>
     <t>TEST ID - 03</t>
@@ -1861,6 +1855,16 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1876,16 +1880,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2177,12 +2171,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" s="1" customFormat="1" ht="86.25" customHeight="1">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -2219,10 +2213,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E3" s="11"/>
     </row>
@@ -2231,10 +2225,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E4" s="11"/>
     </row>
@@ -2243,10 +2237,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E5" s="11"/>
     </row>
@@ -2255,10 +2249,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E6" s="11"/>
     </row>
@@ -2267,10 +2261,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E7" s="11"/>
     </row>
@@ -2279,10 +2273,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E8" s="11"/>
     </row>
@@ -2291,10 +2285,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E9" s="11"/>
     </row>
@@ -2303,10 +2297,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E10" s="11"/>
     </row>
@@ -2315,10 +2309,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E11" s="11"/>
     </row>
@@ -2327,10 +2321,10 @@
         <v>5</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E12" s="11"/>
     </row>
@@ -2339,10 +2333,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E13" s="11"/>
     </row>
@@ -2351,10 +2345,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E14" s="11"/>
     </row>
@@ -2363,10 +2357,10 @@
         <v>5</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E15" s="11"/>
     </row>
@@ -2375,10 +2369,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E16" s="11"/>
     </row>
@@ -2387,10 +2381,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E17" s="11"/>
     </row>
@@ -2399,10 +2393,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E18" s="11"/>
     </row>
@@ -2411,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E19" s="11"/>
     </row>
@@ -2423,10 +2417,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E20" s="11"/>
     </row>
@@ -2435,10 +2429,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E21" s="11"/>
     </row>
@@ -2447,10 +2441,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E22" s="11"/>
     </row>
@@ -2459,10 +2453,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E23" s="11"/>
     </row>
@@ -2471,126 +2465,126 @@
         <v>5</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="2:5" s="40" customFormat="1">
-      <c r="B25" s="37"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="39"/>
-    </row>
-    <row r="26" spans="2:5" s="40" customFormat="1">
-      <c r="B26" s="37"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="39"/>
-    </row>
-    <row r="27" spans="2:5" s="40" customFormat="1">
-      <c r="B27" s="37"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="39"/>
-    </row>
-    <row r="28" spans="2:5" s="40" customFormat="1">
-      <c r="B28" s="37"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="39"/>
-    </row>
-    <row r="29" spans="2:5" s="40" customFormat="1">
-      <c r="B29" s="37"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="39"/>
-    </row>
-    <row r="30" spans="2:5" s="40" customFormat="1">
-      <c r="B30" s="37"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="39"/>
-    </row>
-    <row r="31" spans="2:5" s="40" customFormat="1">
-      <c r="B31" s="37"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="39"/>
-    </row>
-    <row r="32" spans="2:5" s="40" customFormat="1">
-      <c r="B32" s="37"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="39"/>
-    </row>
-    <row r="33" spans="2:5" s="40" customFormat="1">
-      <c r="B33" s="37"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="39"/>
-    </row>
-    <row r="34" spans="2:5" s="40" customFormat="1">
-      <c r="B34" s="37"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="39"/>
-    </row>
-    <row r="35" spans="2:5" s="40" customFormat="1">
-      <c r="B35" s="37"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="39"/>
-    </row>
-    <row r="36" spans="2:5" s="40" customFormat="1">
-      <c r="B36" s="37"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="39"/>
-    </row>
-    <row r="37" spans="2:5" s="40" customFormat="1">
-      <c r="B37" s="37"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="39"/>
-    </row>
-    <row r="38" spans="2:5" s="40" customFormat="1">
-      <c r="B38" s="37"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="39"/>
-    </row>
-    <row r="39" spans="2:5" s="40" customFormat="1">
-      <c r="B39" s="37"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="39"/>
-    </row>
-    <row r="40" spans="2:5" s="40" customFormat="1">
-      <c r="B40" s="37"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="39"/>
-    </row>
-    <row r="41" spans="2:5" s="40" customFormat="1">
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-    </row>
-    <row r="42" spans="2:5" s="40" customFormat="1">
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-    </row>
-    <row r="43" spans="2:5" s="40" customFormat="1">
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="39"/>
+    <row r="25" spans="2:5" s="35" customFormat="1">
+      <c r="B25" s="32"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="34"/>
+    </row>
+    <row r="26" spans="2:5" s="35" customFormat="1">
+      <c r="B26" s="32"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="34"/>
+    </row>
+    <row r="27" spans="2:5" s="35" customFormat="1">
+      <c r="B27" s="32"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="34"/>
+    </row>
+    <row r="28" spans="2:5" s="35" customFormat="1">
+      <c r="B28" s="32"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="34"/>
+    </row>
+    <row r="29" spans="2:5" s="35" customFormat="1">
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="34"/>
+    </row>
+    <row r="30" spans="2:5" s="35" customFormat="1">
+      <c r="B30" s="32"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="34"/>
+    </row>
+    <row r="31" spans="2:5" s="35" customFormat="1">
+      <c r="B31" s="32"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="34"/>
+    </row>
+    <row r="32" spans="2:5" s="35" customFormat="1">
+      <c r="B32" s="32"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="34"/>
+    </row>
+    <row r="33" spans="2:5" s="35" customFormat="1">
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="34"/>
+    </row>
+    <row r="34" spans="2:5" s="35" customFormat="1">
+      <c r="B34" s="32"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="34"/>
+    </row>
+    <row r="35" spans="2:5" s="35" customFormat="1">
+      <c r="B35" s="32"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="34"/>
+    </row>
+    <row r="36" spans="2:5" s="35" customFormat="1">
+      <c r="B36" s="32"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="34"/>
+    </row>
+    <row r="37" spans="2:5" s="35" customFormat="1">
+      <c r="B37" s="32"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="34"/>
+    </row>
+    <row r="38" spans="2:5" s="35" customFormat="1">
+      <c r="B38" s="32"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="34"/>
+    </row>
+    <row r="39" spans="2:5" s="35" customFormat="1">
+      <c r="B39" s="32"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="34"/>
+    </row>
+    <row r="40" spans="2:5" s="35" customFormat="1">
+      <c r="B40" s="32"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="34"/>
+    </row>
+    <row r="41" spans="2:5" s="35" customFormat="1">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+    </row>
+    <row r="42" spans="2:5" s="35" customFormat="1">
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+    </row>
+    <row r="43" spans="2:5" s="35" customFormat="1">
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2609,15 +2603,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="145.5" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13" t="s">
@@ -3153,15 +3147,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="165" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13" t="s">
@@ -3309,16 +3303,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="134.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="13" t="s">
@@ -3351,7 +3345,7 @@
         <v>149</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C3" s="30" t="s">
         <v>127</v>
@@ -3360,27 +3354,27 @@
         <v>150</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="19"/>
       <c r="B4" s="26" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="19"/>
       <c r="E4" s="26" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29">
@@ -3411,14 +3405,14 @@
       <c r="B6" s="19"/>
       <c r="C6" s="31"/>
       <c r="D6" s="26" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:8" ht="29">
       <c r="A7" s="26" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>155</v>
@@ -3444,7 +3438,7 @@
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="D8" s="26" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E8" s="19"/>
       <c r="F8" s="19"/>
@@ -3454,29 +3448,29 @@
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="26" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="58">
       <c r="A10" s="26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H10" t="s">
         <v>21</v>
@@ -3484,22 +3478,22 @@
     </row>
     <row r="11" spans="1:8" ht="58">
       <c r="A11" s="26" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C11" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H11" t="s">
         <v>21</v>
@@ -3507,45 +3501,45 @@
     </row>
     <row r="12" spans="1:8" ht="58">
       <c r="A12" s="26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58">
       <c r="A13" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="F13" s="26" t="s">
         <v>344</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>346</v>
       </c>
       <c r="H13" t="s">
         <v>21</v>
@@ -3553,114 +3547,114 @@
     </row>
     <row r="14" spans="1:8" ht="43.5">
       <c r="A14" s="26" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D14" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="E14" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>335</v>
-      </c>
       <c r="H14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="58">
       <c r="A15" s="26" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>340</v>
-      </c>
       <c r="H15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="58">
       <c r="A16" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C16" t="s">
         <v>127</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E16" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="58">
       <c r="A17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="26" t="s">
+        <v>352</v>
+      </c>
+      <c r="E17" t="s">
+        <v>321</v>
+      </c>
+      <c r="F17" t="s">
+        <v>322</v>
+      </c>
+      <c r="H17" t="s">
         <v>354</v>
-      </c>
-      <c r="E17" t="s">
-        <v>323</v>
-      </c>
-      <c r="F17" t="s">
-        <v>324</v>
-      </c>
-      <c r="H17" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="58">
       <c r="A18" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C18" t="s">
         <v>127</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F18" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H18" t="s">
         <v>21</v>
@@ -3668,22 +3662,22 @@
     </row>
     <row r="19" spans="1:8" ht="58">
       <c r="A19" s="26" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C19" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H19" t="s">
         <v>21</v>
@@ -3691,140 +3685,140 @@
     </row>
     <row r="20" spans="1:8" ht="43.5">
       <c r="A20" s="26" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D20" s="26" t="s">
+        <v>362</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="F20" s="26" t="s">
         <v>364</v>
       </c>
-      <c r="E20" s="26" t="s">
-        <v>365</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>366</v>
-      </c>
       <c r="H20" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="58">
       <c r="A21" s="26" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C21" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="58">
       <c r="A22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C22" t="s">
         <v>127</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F22" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="58">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F23" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H23" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="58">
       <c r="A24" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C24" t="s">
         <v>127</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E24" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F24" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="58">
       <c r="A25" s="26" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C25" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3840,7 +3834,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="31.36328125" customWidth="1"/>
@@ -3848,22 +3842,20 @@
     <col min="4" max="4" width="27.26953125" customWidth="1"/>
     <col min="5" max="5" width="24.453125" customWidth="1"/>
     <col min="6" max="6" width="25.81640625" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="118.5" customHeight="1">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:7" ht="118.5" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
-    </row>
-    <row r="2" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+    </row>
+    <row r="2" spans="1:7" ht="22.5" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
@@ -3882,305 +3874,262 @@
       <c r="F2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="H2" s="17" t="s">
+      <c r="G2" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="29">
+      <c r="A3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="29">
-      <c r="A3" t="s">
+      <c r="B3" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="D3" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>165</v>
-      </c>
       <c r="G3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="29">
+      <c r="A4" t="s">
         <v>166</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
-      <c r="A4" t="s">
+      <c r="B4" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="D4" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="43.5">
+      <c r="A5" t="s">
         <v>170</v>
       </c>
-      <c r="G4" t="s">
+      <c r="B5" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.5">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.5">
+      <c r="A6" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="B6" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.5">
-      <c r="A6" t="s">
+      <c r="D6" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="43.5">
+      <c r="A7" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="B7" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.5">
-      <c r="A7" t="s">
+      <c r="D7" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="19" t="s">
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.5">
+      <c r="A8" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="B8" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.5">
-      <c r="A8" t="s">
+      <c r="D8" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="F8" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="19" t="s">
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
         <v>188</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="B9" s="19" t="s">
         <v>189</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>191</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
     </row>
-    <row r="10" spans="1:8" ht="72.5">
+    <row r="10" spans="1:7" ht="72.5">
       <c r="A10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="E10" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="F10" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="72.5">
+      <c r="A11" t="s">
         <v>195</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="B11" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="G10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="72.5">
-      <c r="A11" t="s">
+      <c r="D11" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="E11" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.5">
+      <c r="A12" t="s">
         <v>199</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="F11" s="19" t="s">
+      <c r="B12" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="43.5">
-      <c r="A12" t="s">
+      <c r="D12" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="F12" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="19" t="s">
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="29">
+      <c r="A13" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="B13" s="19" t="s">
         <v>204</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="29">
-      <c r="A13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>206</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
       </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="29">
+    </row>
+    <row r="14" spans="1:7" ht="29">
       <c r="A14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="E14" t="s">
+        <v>206</v>
+      </c>
+      <c r="F14" t="s">
         <v>207</v>
-      </c>
-      <c r="E14" t="s">
-        <v>208</v>
-      </c>
-      <c r="F14" t="s">
-        <v>209</v>
       </c>
       <c r="G14" t="s">
         <v>53</v>
       </c>
-      <c r="H14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="29">
+    </row>
+    <row r="15" spans="1:7" ht="29">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G15" t="s">
         <v>53</v>
       </c>
-      <c r="H15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="29">
+    </row>
+    <row r="16" spans="1:7" ht="29">
       <c r="A16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G16" t="s">
         <v>53</v>
       </c>
-      <c r="H16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="132" customHeight="1">
-      <c r="A25" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="36"/>
-    </row>
-    <row r="26" spans="1:8">
+    </row>
+    <row r="25" spans="1:7" ht="132" customHeight="1">
+      <c r="A25" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="16" t="s">
         <v>7</v>
       </c>
@@ -4202,237 +4151,210 @@
       <c r="G26" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="72.5">
+    </row>
+    <row r="27" spans="1:7" ht="72.5">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C27" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D27" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F27" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="G27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="72.5">
+      <c r="A28" t="s">
         <v>218</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="B28" s="19" t="s">
         <v>219</v>
-      </c>
-      <c r="G27" t="s">
-        <v>171</v>
-      </c>
-      <c r="H27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="72.5">
-      <c r="A28" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>221</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E28" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="G28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="72.5">
+      <c r="A29" t="s">
         <v>222</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="B29" s="19" t="s">
         <v>223</v>
-      </c>
-      <c r="G28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="72.5">
-      <c r="A29" t="s">
-        <v>224</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>225</v>
       </c>
       <c r="C29" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E29" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="G29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="72.5">
+      <c r="A30" t="s">
         <v>226</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="B30" s="19" t="s">
         <v>227</v>
-      </c>
-      <c r="G29" t="s">
-        <v>171</v>
-      </c>
-      <c r="H29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="72.5">
-      <c r="A30" t="s">
-        <v>228</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>229</v>
       </c>
       <c r="C30" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E30" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="116">
+      <c r="A31" t="s">
         <v>230</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="B31" s="19" t="s">
         <v>231</v>
-      </c>
-      <c r="G30" t="s">
-        <v>171</v>
-      </c>
-      <c r="H30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="116">
-      <c r="A31" t="s">
-        <v>232</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>233</v>
       </c>
       <c r="C31" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D31" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="F31" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="G31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="72.5">
+      <c r="A32" t="s">
         <v>235</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="B32" s="19" t="s">
         <v>236</v>
-      </c>
-      <c r="G31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="72.5">
-      <c r="A32" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>238</v>
       </c>
       <c r="C32" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E32" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="101.5">
+      <c r="A33" t="s">
         <v>239</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="B33" s="19" t="s">
         <v>240</v>
-      </c>
-      <c r="G32" t="s">
-        <v>171</v>
-      </c>
-      <c r="H32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="101.5">
-      <c r="A33" t="s">
-        <v>241</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>242</v>
       </c>
       <c r="C33" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D33" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="101.5">
+      <c r="A34" t="s">
         <v>244</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="B34" s="19" t="s">
         <v>245</v>
-      </c>
-      <c r="G33" t="s">
-        <v>171</v>
-      </c>
-      <c r="H33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="101.5">
-      <c r="A34" t="s">
-        <v>246</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>247</v>
       </c>
       <c r="C34" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D34" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="G34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
         <v>249</v>
       </c>
-      <c r="F34" s="19" t="s">
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
         <v>250</v>
       </c>
-      <c r="G34" t="s">
-        <v>171</v>
-      </c>
-      <c r="H34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4444,15 +4366,15 @@
   <sheetFormatPr defaultColWidth="14.90625" defaultRowHeight="43.5" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:7" ht="129" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="43.5" customHeight="1">
       <c r="A2" s="13" t="s">
@@ -4479,22 +4401,22 @@
     </row>
     <row r="3" spans="1:7" ht="43.5" customHeight="1">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F3" t="s">
         <v>256</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" t="s">
-        <v>258</v>
       </c>
       <c r="G3" t="s">
         <v>21</v>
@@ -4502,19 +4424,19 @@
     </row>
     <row r="4" spans="1:7" ht="43.5" customHeight="1">
       <c r="A4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -4522,19 +4444,19 @@
     </row>
     <row r="5" spans="1:7" ht="43.5" customHeight="1">
       <c r="A5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G5" t="s">
         <v>53</v>
@@ -4542,19 +4464,19 @@
     </row>
     <row r="6" spans="1:7" ht="43.5" customHeight="1">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G6" t="s">
         <v>53</v>
@@ -4562,22 +4484,22 @@
     </row>
     <row r="7" spans="1:7" ht="43.5" customHeight="1">
       <c r="A7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>272</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>274</v>
       </c>
       <c r="G7" t="s">
         <v>53</v>
@@ -4585,22 +4507,22 @@
     </row>
     <row r="8" spans="1:7" ht="43.5" customHeight="1">
       <c r="A8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G8" t="s">
         <v>21</v>
@@ -4629,15 +4551,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="129.75" customHeight="1">
-      <c r="A1" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="A1" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -4664,45 +4586,45 @@
     </row>
     <row r="3" spans="1:7" ht="48" customHeight="1">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D3" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>284</v>
-      </c>
       <c r="G3" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -4710,22 +4632,22 @@
     </row>
     <row r="5" spans="1:7" ht="58">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
@@ -4733,45 +4655,45 @@
     </row>
     <row r="6" spans="1:7" ht="58">
       <c r="A6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.5">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -4779,22 +4701,22 @@
     </row>
     <row r="8" spans="1:7" ht="58">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G8" t="s">
         <v>21</v>
@@ -4802,22 +4724,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
